--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260629.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>25.97%</t>
+          <t>26.09%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.52%</t>
+          <t>8.84%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>7.51%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.03%</t>
+          <t>7.20%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.47%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>36,530</t>
+          <t>21,183</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>21,183</t>
+          <t>36,530</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -880,73 +880,73 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>59,155</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>89,195</t>
+          <t>59,155</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>124,043,363</t>
+          <t>89,195</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>30,798</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>30,798</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>68,868</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>68,868</t>
+          <t>89,066,453</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>147,015</t>
+          <t>21,455</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,455</t>
+          <t>147,015</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1254,73 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,942,745</t>
+          <t>50,090</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>50,090</t>
+          <t>942,745</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>31,854,000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
